--- a/fx_pipeline/data/gold/marts/excel/gold_strength_rankings.xlsx
+++ b/fx_pipeline/data/gold/marts/excel/gold_strength_rankings.xlsx
@@ -413,240 +413,102 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>target_currency</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>weekly_avg</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>weekly_high</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>weekly_low</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>start_rate</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>end_rate</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>weekly_change</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
           <t>weekly_pct_change</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>rank</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.224935297226249</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.1095535398751309</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.07491438356165174</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>JPY</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>159.176</v>
-      </c>
-      <c r="C2" t="n">
-        <v>159.83</v>
-      </c>
-      <c r="D2" t="n">
-        <v>158.85</v>
-      </c>
-      <c r="E2" t="n">
-        <v>159.83</v>
-      </c>
-      <c r="F2" t="n">
-        <v>159.13</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-0.7000000000000171</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-0.4379653381718182</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>93.184</v>
-      </c>
-      <c r="C3" t="n">
-        <v>93.44</v>
-      </c>
-      <c r="D3" t="n">
-        <v>92.81999999999999</v>
-      </c>
-      <c r="E3" t="n">
-        <v>93.33</v>
-      </c>
-      <c r="F3" t="n">
-        <v>92.81999999999999</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-0.5100000000000051</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-0.5464480874316995</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.739468</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.7451</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.73699</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.7451</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.7389</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-0.006199999999999983</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-0.8321030734129625</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.8498300000000001</v>
-      </c>
       <c r="C5" t="n">
-        <v>0.85587</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.84767</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.85587</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.84767</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-0.008199999999999985</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-0.958089429469427</v>
-      </c>
-      <c r="I5" t="n">
-        <v>4</v>
+        <v>-0.03142875102144155</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.3996289160065688</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>CAD</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>1.3757</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1.3845</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1.3672</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1.3845</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.3672</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-0.01730000000000009</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-1.249548573492242</v>
-      </c>
-      <c r="I6" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>AUD</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1.4029</v>
-      </c>
       <c r="C7" t="n">
-        <v>1.4216</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1.3934</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1.4216</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.3934</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-0.0282</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-1.983680360157569</v>
-      </c>
-      <c r="I7" t="n">
-        <v>6</v>
+        <v>-0.9069801189958044</v>
       </c>
     </row>
   </sheetData>
